--- a/output_transformed.xlsx
+++ b/output_transformed.xlsx
@@ -18,36 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="新宋体"/>
-      <b val="1"/>
-      <sz val="30"/>
-    </font>
-    <font>
-      <name val="新宋体"/>
-      <b val="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="新宋体"/>
-      <b val="1"/>
-      <sz val="26"/>
-    </font>
-    <font>
-      <name val="新宋体"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="新宋体"/>
-      <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -59,7 +36,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -68,50 +45,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6F3FF"/>
-        <bgColor rgb="FFE6F3FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E6F3FF"/>
         <bgColor rgb="00E6F3FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5E8"/>
-        <bgColor rgb="FFE8F5E8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF9E6"/>
-        <bgColor rgb="FFFFF9E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4EC"/>
-        <bgColor rgb="FFFCE4EC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3E5F5"/>
-        <bgColor rgb="FFF3E5F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3E0"/>
-        <bgColor rgb="FFFFF3E0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2F1"/>
-        <bgColor rgb="FFE0F2F1"/>
       </patternFill>
     </fill>
   </fills>
@@ -133,60 +68,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -554,274 +441,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="45" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>应用變更人員時間安排表0521</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="35" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>執行人員</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>5月18日</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>5月20日</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>5月21日</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>5月23日</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>5月24日</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>18:00 至 18:30</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>18:00 至 19:00</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>18:00 至 20:00</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>10:00 至 11:30</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>01:30</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>02:00</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>03:00</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="80" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>李俊毅</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>2392 CAP 何幗蕙</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>2383 CCM 晏鵬禹</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>2381 DWS 王文斌</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="80" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>岑惠韜</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>2386 MHR 林秋明</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>2380 MEG 何文俊</t>
-        </is>
-      </c>
-      <c r="L5" s="8" t="inlineStr">
-        <is>
-          <t>2367 GBS 葉俊濠</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="80" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>羅家勝</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>2390 Unknown 李鈞朗</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>2378 PDP 黃昕</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>2382 DBP 黃君豪</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="80" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>曠森</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>2376 CMP 何文俊</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>2374 STS 顏黛雯</t>
-        </is>
-      </c>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>2307 DDP 何子楓</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="80" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>李曼菁</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>2388 CAP 沈彪
-2384 AAS 張雋宇</t>
-        </is>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>2331 DBP 黃君豪</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="80" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>黃靖雲</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>2363 ESG 覃福康
-2362 IXP 覃福康
-2358 MFT 沈彪
-2330 DWS 葉俊濠</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>2321 ADC 林秋明</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>2385 AAS 張雋宇</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="F9:K9"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="G8:K8"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="F2:N2"/>
-    <mergeCell ref="A1:N1"/>
-  </mergeCells>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -869,202 +491,202 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>工單號</t>
         </is>
       </c>
-      <c r="B1" s="17" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>工单状态</t>
         </is>
       </c>
-      <c r="C1" s="17" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>提單人</t>
         </is>
       </c>
-      <c r="D1" s="17" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>提單時間</t>
         </is>
       </c>
-      <c r="E1" s="17" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>提單日期</t>
         </is>
       </c>
-      <c r="F1" s="17" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>提單人部門</t>
         </is>
       </c>
-      <c r="G1" s="17" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>提單人所屬團隊</t>
         </is>
       </c>
-      <c r="H1" s="17" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>變更名稱</t>
         </is>
       </c>
-      <c r="I1" s="17" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>變更具體描述</t>
         </is>
       </c>
-      <c r="J1" s="17" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>變更類型</t>
         </is>
       </c>
-      <c r="K1" s="17" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>變更分類</t>
         </is>
       </c>
-      <c r="L1" s="17" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>來源類型</t>
         </is>
       </c>
-      <c r="M1" s="17" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>關聯工單號</t>
         </is>
       </c>
-      <c r="N1" s="17" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>使用ID</t>
         </is>
       </c>
-      <c r="O1" s="17" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>計劃開始時間</t>
         </is>
       </c>
-      <c r="P1" s="17" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>計劃結束時間</t>
         </is>
       </c>
-      <c r="Q1" s="17" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>變更系統名稱匯總</t>
         </is>
       </c>
-      <c r="R1" s="17" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>變更是否在窗口內</t>
         </is>
       </c>
-      <c r="S1" s="17" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>是否與總行同步變更</t>
         </is>
       </c>
-      <c r="T1" s="17" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>業務聯繫人</t>
         </is>
       </c>
-      <c r="U1" s="17" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>是否影響服務</t>
         </is>
       </c>
-      <c r="V1" s="17" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>影響服務開始時間</t>
         </is>
       </c>
-      <c r="W1" s="17" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>影響服務結束時間</t>
         </is>
       </c>
-      <c r="X1" s="17" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>影響服務時間（分鐘）</t>
         </is>
       </c>
-      <c r="Y1" s="17" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>影響服務的範圍</t>
         </is>
       </c>
-      <c r="Z1" s="17" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>是否公示</t>
         </is>
       </c>
-      <c r="AA1" s="17" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>本部門參與團隊</t>
         </is>
       </c>
-      <c r="AB1" s="17" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>變更配合部門</t>
         </is>
       </c>
-      <c r="AC1" s="17" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>變更關閉日期</t>
         </is>
       </c>
-      <c r="AD1" s="17" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>是否涉及回退</t>
         </is>
       </c>
-      <c r="AE1" s="17" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>當前步驟</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>MOBG-2026-02392</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>何幗蕙/mo171492</t>
         </is>
       </c>
-      <c r="D2" s="18" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>2026-05-18 14:07:49</t>
         </is>
       </c>
-      <c r="E2" s="18" t="n">
-        <v/>
-      </c>
-      <c r="F2" s="18" t="inlineStr">
+      <c r="E2" s="2" t="n">
+        <v/>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>資訊科技部</t>
         </is>
       </c>
-      <c r="G2" s="18" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>系統開發四團隊</t>
         </is>
       </c>
-      <c r="H2" s="18" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>CAP開發框架TRP跑批異常處理</t>
         </is>
       </c>
-      <c r="I2" s="18" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>變更原因：CAP開發框架因05/18 148 TRP檔案缺失導致跑批失敗
 變更主要內容：於調度平台刪除失敗任務並重跑CAP-TRP 148批量
@@ -1076,381 +698,381 @@
 調度平台-&gt;監控管理-&gt;任務監控-&gt;特色對賬組件，刪除處理對賬文件-148失敗任務後，重跑處理對賬文件-148任務</t>
         </is>
       </c>
-      <c r="J2" s="18" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>普通變更</t>
         </is>
       </c>
-      <c r="K2" s="18" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>應用-&gt;其他變更</t>
         </is>
       </c>
-      <c r="L2" s="18" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>請求</t>
         </is>
       </c>
-      <c r="M2" s="18" t="n">
-        <v/>
-      </c>
-      <c r="N2" s="18" t="n">
-        <v/>
-      </c>
-      <c r="O2" s="18" t="inlineStr">
+      <c r="M2" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>2026-05-18 18:00:00</t>
         </is>
       </c>
-      <c r="P2" s="18" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>2026-05-18 18:30:00</t>
         </is>
       </c>
-      <c r="Q2" s="18" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>CAP-公共應用平臺</t>
         </is>
       </c>
-      <c r="R2" s="18" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="S2" s="18" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="T2" s="18" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="18" t="inlineStr">
+      <c r="T2" s="2" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="V2" s="18" t="n">
-        <v/>
-      </c>
-      <c r="W2" s="18" t="n">
-        <v/>
-      </c>
-      <c r="X2" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Y2" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Z2" s="18" t="inlineStr">
+      <c r="V2" s="2" t="n">
+        <v/>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v/>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Y2" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA2" s="18" t="inlineStr">
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>中國銀行澳門分行/資訊科技部/系統開發四團隊,中國銀行澳門分行/資訊科技部/應用運維團隊</t>
         </is>
       </c>
-      <c r="AB2" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AC2" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AD2" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AE2" s="18" t="inlineStr">
+      <c r="AB2" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AC2" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AD2" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
         <is>
           <t>一級變更經理審批</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>MOBG-2026-02390</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>李鈞朗/mo162213</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>2026-05-18 09:21:28</t>
         </is>
       </c>
-      <c r="E3" s="18" t="n">
-        <v/>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="E3" s="2" t="n">
+        <v/>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>資訊科技部</t>
         </is>
       </c>
-      <c r="G3" s="18" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>系統開發五團隊</t>
         </is>
       </c>
-      <c r="H3" s="18" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>中銀e網(企業)週期功能bugfix</t>
         </is>
       </c>
-      <c r="I3" s="18" t="n">
-        <v/>
-      </c>
-      <c r="J3" s="18" t="inlineStr">
+      <c r="I3" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>普通變更</t>
         </is>
       </c>
-      <c r="K3" s="18" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>應用-&gt;應用產品投產</t>
         </is>
       </c>
-      <c r="L3" s="18" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="18" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="18" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="18" t="inlineStr">
+      <c r="L3" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>2026-05-20 18:00:00</t>
         </is>
       </c>
-      <c r="P3" s="18" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>2026-05-20 18:30:00</t>
         </is>
       </c>
-      <c r="Q3" s="18" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="18" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="18" t="inlineStr">
+      <c r="Q3" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="T3" s="18" t="inlineStr">
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>張麗芳/mo143430</t>
         </is>
       </c>
-      <c r="U3" s="18" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="18" t="n">
-        <v/>
-      </c>
-      <c r="W3" s="18" t="n">
-        <v/>
-      </c>
-      <c r="X3" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Y3" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Z3" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AA3" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AB3" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AC3" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AD3" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AE3" s="18" t="inlineStr">
+      <c r="U3" s="2" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v/>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v/>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Y3" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AB3" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AC3" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AD3" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AE3" s="2" t="inlineStr">
         <is>
           <t>正式填報</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>MOBG-2026-02388</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>沈彪/mo171026</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>2026-05-17 02:39:16</t>
         </is>
       </c>
-      <c r="E4" s="18" t="n">
-        <v/>
-      </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="E4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>資訊科技部</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>系統開發四團隊</t>
         </is>
       </c>
-      <c r="H4" s="18" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>CAP配合電服團隊修改GZCK,GDCK,GDMK角色權限需求投產</t>
         </is>
       </c>
-      <c r="I4" s="18" t="n">
-        <v/>
-      </c>
-      <c r="J4" s="18" t="inlineStr">
+      <c r="I4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>普通變更</t>
         </is>
       </c>
-      <c r="K4" s="18" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>應用-&gt;應用產品投產</t>
         </is>
       </c>
-      <c r="L4" s="18" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="18" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="18" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="18" t="inlineStr">
+      <c r="L4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>2026-05-21 18:00:00</t>
         </is>
       </c>
-      <c r="P4" s="18" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>2026-05-21 19:00:00</t>
         </is>
       </c>
-      <c r="Q4" s="18" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="18" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="18" t="inlineStr">
+      <c r="Q4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="T4" s="18" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="18" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="18" t="n">
-        <v/>
-      </c>
-      <c r="W4" s="18" t="n">
-        <v/>
-      </c>
-      <c r="X4" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Y4" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Z4" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AA4" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AB4" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AC4" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AD4" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AE4" s="18" t="inlineStr">
+      <c r="T4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="X4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Y4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AA4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AB4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AC4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AD4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AE4" s="2" t="inlineStr">
         <is>
           <t>正式填報</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>MOBG-2026-02386</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>林秋明/mo142409</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>2026-05-15 17:33:38</t>
         </is>
       </c>
-      <c r="E5" s="18" t="n">
-        <v/>
-      </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="E5" s="2" t="n">
+        <v/>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>資訊科技部</t>
         </is>
       </c>
-      <c r="G5" s="18" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>系統開發二團隊</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>MHR系统关于配合獵手中台下傳數據的需求投产</t>
         </is>
       </c>
-      <c r="I5" s="18" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>變更原因：調整下傳數據
 變更主要內容：組織人事
@@ -1460,1238 +1082,1238 @@
 漏洞扫描情况（新增服务器、系统和中间件升级等变更请提前联系安全团队进行漏洞扫描）不涉及</t>
         </is>
       </c>
-      <c r="J5" s="18" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>普通變更</t>
         </is>
       </c>
-      <c r="K5" s="18" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>應用-&gt;應用產品投產</t>
         </is>
       </c>
-      <c r="L5" s="18" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>任務</t>
         </is>
       </c>
-      <c r="M5" s="18" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="18" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="18" t="inlineStr">
+      <c r="M5" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>2026-05-18 18:00:00</t>
         </is>
       </c>
-      <c r="P5" s="18" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>2026-05-18 18:15:00</t>
         </is>
       </c>
-      <c r="Q5" s="18" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>MHR-人事綜合管理系統</t>
         </is>
       </c>
-      <c r="R5" s="18" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="S5" s="18" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="T5" s="18" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
         <is>
           <t>李曼菁/mo169536</t>
         </is>
       </c>
-      <c r="U5" s="18" t="inlineStr">
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="V5" s="18" t="n">
-        <v/>
-      </c>
-      <c r="W5" s="18" t="n">
-        <v/>
-      </c>
-      <c r="X5" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Y5" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Z5" s="18" t="inlineStr">
+      <c r="V5" s="2" t="n">
+        <v/>
+      </c>
+      <c r="W5" s="2" t="n">
+        <v/>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA5" s="18" t="inlineStr">
+      <c r="AA5" s="2" t="inlineStr">
         <is>
           <t>中國銀行澳門分行/資訊科技部/應用運維團隊</t>
         </is>
       </c>
-      <c r="AB5" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AC5" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AD5" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AE5" s="18" t="inlineStr">
+      <c r="AB5" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AC5" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AD5" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
         <is>
           <t>執行人員指派</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>MOBG-2026-02385</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>張雋宇/mo159492</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>2026-05-15 17:27:57</t>
         </is>
       </c>
-      <c r="E6" s="18" t="n">
-        <v/>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="E6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>資訊科技部</t>
         </is>
       </c>
-      <c r="G6" s="18" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>系統開發三團隊</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>AAS系统关于配合手機銀行沙盒2的需求投产的变更</t>
         </is>
       </c>
-      <c r="I6" s="18" t="n">
-        <v/>
-      </c>
-      <c r="J6" s="18" t="inlineStr">
+      <c r="I6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>普通變更</t>
         </is>
       </c>
-      <c r="K6" s="18" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>應用-&gt;應用產品投產</t>
         </is>
       </c>
-      <c r="L6" s="18" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="18" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="18" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="18" t="inlineStr">
+      <c r="L6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>2026-05-24 00:30:00</t>
         </is>
       </c>
-      <c r="P6" s="18" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>2026-05-24 06:00:00</t>
         </is>
       </c>
-      <c r="Q6" s="18" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="18" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="18" t="inlineStr">
+      <c r="Q6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="T6" s="18" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="18" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="18" t="n">
-        <v/>
-      </c>
-      <c r="W6" s="18" t="n">
-        <v/>
-      </c>
-      <c r="X6" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Y6" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Z6" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AA6" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AB6" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AC6" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AD6" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AE6" s="18" t="inlineStr">
+      <c r="T6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Y6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AB6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AC6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AD6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AE6" s="2" t="inlineStr">
         <is>
           <t>正式填報</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>MOBG-2026-02384</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>張雋宇/mo159492</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>2026-05-15 17:26:14</t>
         </is>
       </c>
-      <c r="E7" s="18" t="n">
-        <v/>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="E7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>資訊科技部</t>
         </is>
       </c>
-      <c r="G7" s="18" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>系統開發三團隊</t>
         </is>
       </c>
-      <c r="H7" s="18" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>AAS系统关于加密機接入生產的变更</t>
         </is>
       </c>
-      <c r="I7" s="18" t="n">
-        <v/>
-      </c>
-      <c r="J7" s="18" t="inlineStr">
+      <c r="I7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>普通變更</t>
         </is>
       </c>
-      <c r="K7" s="18" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>應用-&gt;應用產品投產</t>
         </is>
       </c>
-      <c r="L7" s="18" t="n">
-        <v/>
-      </c>
-      <c r="M7" s="18" t="n">
-        <v/>
-      </c>
-      <c r="N7" s="18" t="n">
-        <v/>
-      </c>
-      <c r="O7" s="18" t="inlineStr">
+      <c r="L7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>2026-05-21 18:00:00</t>
         </is>
       </c>
-      <c r="P7" s="18" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>2026-05-21 19:30:00</t>
         </is>
       </c>
-      <c r="Q7" s="18" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="18" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="18" t="inlineStr">
+      <c r="Q7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="T7" s="18" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="18" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="18" t="n">
-        <v/>
-      </c>
-      <c r="W7" s="18" t="n">
-        <v/>
-      </c>
-      <c r="X7" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Y7" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Z7" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AA7" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AB7" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AC7" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AD7" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AE7" s="18" t="inlineStr">
+      <c r="T7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Y7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AB7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AC7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AD7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AE7" s="2" t="inlineStr">
         <is>
           <t>正式填報</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>MOBG-2026-02383</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>晏鵬禹/mo147320</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>2026-05-15 17:14:36</t>
         </is>
       </c>
-      <c r="E8" s="18" t="n">
-        <v/>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="E8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>資訊科技部</t>
         </is>
       </c>
-      <c r="G8" s="18" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>系統開發二團隊</t>
         </is>
       </c>
-      <c r="H8" s="18" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>CCM系统关于redis配置密码的需求投产</t>
         </is>
       </c>
-      <c r="I8" s="18" t="n">
-        <v/>
-      </c>
-      <c r="J8" s="18" t="inlineStr">
+      <c r="I8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>普通變更</t>
         </is>
       </c>
-      <c r="K8" s="18" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>系統-&gt;系統補丁安裝</t>
         </is>
       </c>
-      <c r="L8" s="18" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="18" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="18" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="18" t="inlineStr">
+      <c r="L8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>2026-05-21 18:00:00</t>
         </is>
       </c>
-      <c r="P8" s="18" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>2026-05-21 19:00:00</t>
         </is>
       </c>
-      <c r="Q8" s="18" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>CCM-公司客戶關係管理系統</t>
         </is>
       </c>
-      <c r="R8" s="18" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="18" t="inlineStr">
+      <c r="R8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="T8" s="18" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="18" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="18" t="n">
-        <v/>
-      </c>
-      <c r="W8" s="18" t="n">
-        <v/>
-      </c>
-      <c r="X8" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Y8" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Z8" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AA8" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AB8" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AC8" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AD8" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AE8" s="18" t="inlineStr">
+      <c r="T8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AB8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AC8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AD8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AE8" s="2" t="inlineStr">
         <is>
           <t>正式填報</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>MOBG-2026-02382</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>黃君豪/mo159832</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>2026-05-15 16:13:59</t>
         </is>
       </c>
-      <c r="E9" s="18" t="n">
-        <v/>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="E9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>資訊科技部</t>
         </is>
       </c>
-      <c r="G9" s="18" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>系統開發五團隊</t>
         </is>
       </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>配合安全升級, 申請渠道系統重啟應用及修改密碼的变更</t>
         </is>
       </c>
-      <c r="I9" s="18" t="n">
-        <v/>
-      </c>
-      <c r="J9" s="18" t="inlineStr">
+      <c r="I9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>普通變更</t>
         </is>
       </c>
-      <c r="K9" s="18" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>系統-&gt;其他變更</t>
         </is>
       </c>
-      <c r="L9" s="18" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="18" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="18" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="18" t="inlineStr">
+      <c r="L9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>2026-05-24 02:00:00</t>
         </is>
       </c>
-      <c r="P9" s="18" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>2026-05-24 06:00:00</t>
         </is>
       </c>
-      <c r="Q9" s="18" t="inlineStr">
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>DBP-手機銀行,MPS-消息推送系統,WXS-微信銀行</t>
         </is>
       </c>
-      <c r="R9" s="18" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="18" t="inlineStr">
+      <c r="R9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="T9" s="18" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="18" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="18" t="n">
-        <v/>
-      </c>
-      <c r="W9" s="18" t="n">
-        <v/>
-      </c>
-      <c r="X9" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Y9" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Z9" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AA9" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AB9" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AC9" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AD9" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AE9" s="18" t="inlineStr">
+      <c r="T9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="W9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Y9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AA9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AB9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AC9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AD9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AE9" s="2" t="inlineStr">
         <is>
           <t>正式填報</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>MOBG-2026-02381</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>王文斌/mo146714</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>2026-05-15 16:06:43</t>
         </is>
       </c>
-      <c r="E10" s="18" t="n">
-        <v/>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="E10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>資訊科技部</t>
         </is>
       </c>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>系統開發二團隊</t>
         </is>
       </c>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>數據子集DWS配合沙盒二項目變更</t>
         </is>
       </c>
-      <c r="I10" s="18" t="n">
-        <v/>
-      </c>
-      <c r="J10" s="18" t="inlineStr">
+      <c r="I10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>普通變更</t>
         </is>
       </c>
-      <c r="K10" s="18" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>應用-&gt;應用產品投產</t>
         </is>
       </c>
-      <c r="L10" s="18" t="n">
-        <v/>
-      </c>
-      <c r="M10" s="18" t="n">
-        <v/>
-      </c>
-      <c r="N10" s="18" t="n">
-        <v/>
-      </c>
-      <c r="O10" s="18" t="inlineStr">
+      <c r="L10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>2026-05-24 18:00:00</t>
         </is>
       </c>
-      <c r="P10" s="18" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>2026-05-24 19:00:00</t>
         </is>
       </c>
-      <c r="Q10" s="18" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>DWS-數據子集</t>
         </is>
       </c>
-      <c r="R10" s="18" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="18" t="inlineStr">
+      <c r="R10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="T10" s="18" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="18" t="n">
-        <v/>
-      </c>
-      <c r="V10" s="18" t="n">
-        <v/>
-      </c>
-      <c r="W10" s="18" t="n">
-        <v/>
-      </c>
-      <c r="X10" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Y10" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Z10" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AA10" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AB10" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AC10" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AD10" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AE10" s="18" t="inlineStr">
+      <c r="T10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="W10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Y10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Z10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AA10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AB10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AC10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AD10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AE10" s="2" t="inlineStr">
         <is>
           <t>正式填報</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>MOBG-2026-02380</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>何文俊/mo159557</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>2026-05-15 16:02:53</t>
         </is>
       </c>
-      <c r="E11" s="18" t="n">
-        <v/>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="E11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>資訊科技部</t>
         </is>
       </c>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>系統開發四團隊</t>
         </is>
       </c>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>MEG系统关于Linux漏洞修復的需求投产</t>
         </is>
       </c>
-      <c r="I11" s="18" t="n">
-        <v/>
-      </c>
-      <c r="J11" s="18" t="inlineStr">
+      <c r="I11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>普通變更</t>
         </is>
       </c>
-      <c r="K11" s="18" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>系統-&gt;系統補丁安裝</t>
         </is>
       </c>
-      <c r="L11" s="18" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="18" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="18" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="18" t="inlineStr">
+      <c r="L11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>2026-05-21 18:00:00</t>
         </is>
       </c>
-      <c r="P11" s="18" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>2026-05-21 19:00:00</t>
         </is>
       </c>
-      <c r="Q11" s="18" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="18" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="18" t="inlineStr">
+      <c r="Q11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="T11" s="18" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="18" t="n">
-        <v/>
-      </c>
-      <c r="V11" s="18" t="n">
-        <v/>
-      </c>
-      <c r="W11" s="18" t="n">
-        <v/>
-      </c>
-      <c r="X11" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Y11" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Z11" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AA11" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AB11" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AC11" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AD11" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AE11" s="18" t="inlineStr">
+      <c r="T11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="W11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="X11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Y11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Z11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AA11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AB11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AC11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AD11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AE11" s="2" t="inlineStr">
         <is>
           <t>正式填報</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>MOBG-2026-02378</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>黃昕/mo163430</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>2026-05-15 15:52:03</t>
         </is>
       </c>
-      <c r="E12" s="18" t="n">
-        <v/>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="E12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>資訊科技部</t>
         </is>
       </c>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>系統開發五團隊</t>
         </is>
       </c>
-      <c r="H12" s="18" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>PDP系統關於添加redis密碼的变更</t>
         </is>
       </c>
-      <c r="I12" s="18" t="n">
-        <v/>
-      </c>
-      <c r="J12" s="18" t="inlineStr">
+      <c r="I12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>普通變更</t>
         </is>
       </c>
-      <c r="K12" s="18" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>系統-&gt;其他變更</t>
         </is>
       </c>
-      <c r="L12" s="18" t="n">
-        <v/>
-      </c>
-      <c r="M12" s="18" t="n">
-        <v/>
-      </c>
-      <c r="N12" s="18" t="n">
-        <v/>
-      </c>
-      <c r="O12" s="18" t="inlineStr">
+      <c r="L12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>2026-05-21 18:00:00</t>
         </is>
       </c>
-      <c r="P12" s="18" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>2026-05-21 19:00:00</t>
         </is>
       </c>
-      <c r="Q12" s="18" t="inlineStr">
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>PDP-手機銀行產品管理平臺</t>
         </is>
       </c>
-      <c r="R12" s="18" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="18" t="inlineStr">
+      <c r="R12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="T12" s="18" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="18" t="n">
-        <v/>
-      </c>
-      <c r="V12" s="18" t="n">
-        <v/>
-      </c>
-      <c r="W12" s="18" t="n">
-        <v/>
-      </c>
-      <c r="X12" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Y12" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Z12" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AA12" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AB12" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AC12" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AD12" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AE12" s="18" t="inlineStr">
+      <c r="T12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="W12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="X12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Y12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Z12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AA12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AB12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AC12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AD12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AE12" s="2" t="inlineStr">
         <is>
           <t>正式填報</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>MOBG-2026-02376</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>何文俊/mo159557</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>2026-05-15 15:13:28</t>
         </is>
       </c>
-      <c r="E13" s="18" t="n">
-        <v/>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="E13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>資訊科技部</t>
         </is>
       </c>
-      <c r="G13" s="18" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>系統開發四團隊</t>
         </is>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>CMP系统关于DB2 Linux漏洞修復的需求投产</t>
         </is>
       </c>
-      <c r="I13" s="18" t="n">
-        <v/>
-      </c>
-      <c r="J13" s="18" t="inlineStr">
+      <c r="I13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>普通變更</t>
         </is>
       </c>
-      <c r="K13" s="18" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>系統-&gt;系統補丁安裝</t>
         </is>
       </c>
-      <c r="L13" s="18" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="18" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="18" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="18" t="inlineStr">
+      <c r="L13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>2026-05-20 18:00:00</t>
         </is>
       </c>
-      <c r="P13" s="18" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>2026-05-20 19:00:00</t>
         </is>
       </c>
-      <c r="Q13" s="18" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="18" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="18" t="inlineStr">
+      <c r="Q13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="T13" s="18" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
         <is>
           <t>詹麗瑩/mo156213</t>
         </is>
       </c>
-      <c r="U13" s="18" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="18" t="n">
-        <v/>
-      </c>
-      <c r="W13" s="18" t="n">
-        <v/>
-      </c>
-      <c r="X13" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Y13" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Z13" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AA13" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AB13" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AC13" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AD13" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AE13" s="18" t="inlineStr">
+      <c r="U13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="W13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="X13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Y13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Z13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AA13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AB13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AC13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AD13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AE13" s="2" t="inlineStr">
         <is>
           <t>正式填報</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>MOBG-2026-02374</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>顏黛雯/mo167690</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>2026-05-15 14:10:42</t>
         </is>
       </c>
-      <c r="E14" s="18" t="n">
-        <v/>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="E14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>資訊科技部</t>
         </is>
       </c>
-      <c r="G14" s="18" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>系統開發一團隊</t>
         </is>
       </c>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>STS系统关于導出FIQ子集檔報錯問題修復的變更</t>
         </is>
       </c>
-      <c r="I14" s="18" t="n">
-        <v/>
-      </c>
-      <c r="J14" s="18" t="inlineStr">
+      <c r="I14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>普通變更</t>
         </is>
       </c>
-      <c r="K14" s="18" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>應用-&gt;應用產品投產</t>
         </is>
       </c>
-      <c r="L14" s="18" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="18" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="18" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="18" t="inlineStr">
+      <c r="L14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>2026-05-21 18:00:00</t>
         </is>
       </c>
-      <c r="P14" s="18" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>2026-05-21 19:00:00</t>
         </is>
       </c>
-      <c r="Q14" s="18" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="18" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="18" t="inlineStr">
+      <c r="Q14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="T14" s="18" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="18" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="18" t="n">
-        <v/>
-      </c>
-      <c r="W14" s="18" t="n">
-        <v/>
-      </c>
-      <c r="X14" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Y14" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Z14" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AA14" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AB14" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AC14" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AD14" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AE14" s="18" t="inlineStr">
+      <c r="T14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="W14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="X14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Y14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Z14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AA14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AB14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AC14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AD14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AE14" s="2" t="inlineStr">
         <is>
           <t>正式填報</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>MOBG-2026-02367</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>葉俊濠/mo174319</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>2026-05-15 09:50:09</t>
         </is>
       </c>
-      <c r="E15" s="18" t="n">
-        <v/>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="E15" s="2" t="n">
+        <v/>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>資訊科技部</t>
         </is>
       </c>
-      <c r="G15" s="18" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>系統開發二團隊</t>
         </is>
       </c>
-      <c r="H15" s="18" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>GBS系统关于配合沙盒二BOCPAY項目的变更</t>
         </is>
       </c>
-      <c r="I15" s="18" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>變更原因：配合沙盒二BOCPAY項目加表
 變更主要內容：將新增表配進GBS的調度平台
@@ -2701,627 +2323,627 @@
 漏洞扫描情况（新增服务器、系统和中间件升级等变更请提前联系安全团队进行漏洞扫描）</t>
         </is>
       </c>
-      <c r="J15" s="18" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>普通變更</t>
         </is>
       </c>
-      <c r="K15" s="18" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>應用-&gt;應用產品投產</t>
         </is>
       </c>
-      <c r="L15" s="18" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>任務</t>
         </is>
       </c>
-      <c r="M15" s="18" t="n">
-        <v/>
-      </c>
-      <c r="N15" s="18" t="n">
-        <v/>
-      </c>
-      <c r="O15" s="18" t="inlineStr">
+      <c r="M15" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>2026-05-24 18:00:00</t>
         </is>
       </c>
-      <c r="P15" s="18" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>2026-05-24 18:30:00</t>
         </is>
       </c>
-      <c r="Q15" s="18" t="inlineStr">
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>GBS-GBASE大數據平台</t>
         </is>
       </c>
-      <c r="R15" s="18" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="S15" s="18" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="T15" s="18" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="18" t="inlineStr">
+      <c r="T15" s="2" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="V15" s="18" t="n">
-        <v/>
-      </c>
-      <c r="W15" s="18" t="n">
-        <v/>
-      </c>
-      <c r="X15" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Y15" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Z15" s="18" t="inlineStr">
+      <c r="V15" s="2" t="n">
+        <v/>
+      </c>
+      <c r="W15" s="2" t="n">
+        <v/>
+      </c>
+      <c r="X15" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Y15" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA15" s="18" t="inlineStr">
+      <c r="AA15" s="2" t="inlineStr">
         <is>
           <t>中國銀行澳門分行/資訊科技部/應用運維團隊</t>
         </is>
       </c>
-      <c r="AB15" s="18" t="inlineStr">
+      <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>中國銀行澳門分行/資訊科技部/系統開發二團隊</t>
         </is>
       </c>
-      <c r="AC15" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AD15" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AE15" s="18" t="inlineStr">
+      <c r="AC15" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AD15" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AE15" s="2" t="inlineStr">
         <is>
           <t>正式填報</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>MOBG-2026-02363</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>覃福康/mo162922</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>2026-05-15 09:39:01</t>
         </is>
       </c>
-      <c r="E16" s="18" t="n">
-        <v/>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="E16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>資訊科技部</t>
         </is>
       </c>
-      <c r="G16" s="18" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>系統開發四團隊</t>
         </is>
       </c>
-      <c r="H16" s="18" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>ESG系统关于退場AMCM E-BILLING服務及進行x86服務器OS補丁升級的變更</t>
         </is>
       </c>
-      <c r="I16" s="18" t="n">
-        <v/>
-      </c>
-      <c r="J16" s="18" t="inlineStr">
+      <c r="I16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>普通變更</t>
         </is>
       </c>
-      <c r="K16" s="18" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>應用-&gt;應用產品投產</t>
         </is>
       </c>
-      <c r="L16" s="18" t="n">
-        <v/>
-      </c>
-      <c r="M16" s="18" t="n">
-        <v/>
-      </c>
-      <c r="N16" s="18" t="n">
-        <v/>
-      </c>
-      <c r="O16" s="18" t="inlineStr">
+      <c r="L16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>2026-05-21 18:00:16</t>
         </is>
       </c>
-      <c r="P16" s="18" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>2026-05-21 19:00:54</t>
         </is>
       </c>
-      <c r="Q16" s="18" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>ESG-對外服務網關</t>
         </is>
       </c>
-      <c r="R16" s="18" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="18" t="inlineStr">
+      <c r="R16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="T16" s="18" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="18" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="18" t="n">
-        <v/>
-      </c>
-      <c r="W16" s="18" t="n">
-        <v/>
-      </c>
-      <c r="X16" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Y16" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Z16" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AA16" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AB16" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AC16" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AD16" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AE16" s="18" t="inlineStr">
+      <c r="T16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="W16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="X16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Y16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Z16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AA16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AB16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AC16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AD16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AE16" s="2" t="inlineStr">
         <is>
           <t>正式填報</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>MOBG-2026-02362</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>覃福康/mo162922</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>2026-05-15 09:36:23</t>
         </is>
       </c>
-      <c r="E17" s="18" t="n">
-        <v/>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="E17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>資訊科技部</t>
         </is>
       </c>
-      <c r="G17" s="18" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>系統開發四團隊</t>
         </is>
       </c>
-      <c r="H17" s="18" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>IXP系统关于配合總行T-HIBS下綫創建經T-MSC對接SMSP通道的變更</t>
         </is>
       </c>
-      <c r="I17" s="18" t="n">
-        <v/>
-      </c>
-      <c r="J17" s="18" t="inlineStr">
+      <c r="I17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>普通變更</t>
         </is>
       </c>
-      <c r="K17" s="18" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>應用-&gt;應用產品投產</t>
         </is>
       </c>
-      <c r="L17" s="18" t="n">
-        <v/>
-      </c>
-      <c r="M17" s="18" t="n">
-        <v/>
-      </c>
-      <c r="N17" s="18" t="n">
-        <v/>
-      </c>
-      <c r="O17" s="18" t="inlineStr">
+      <c r="L17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>2026-05-21 18:00:16</t>
         </is>
       </c>
-      <c r="P17" s="18" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>2026-05-21 20:00:54</t>
         </is>
       </c>
-      <c r="Q17" s="18" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="18" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="18" t="inlineStr">
+      <c r="Q17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="T17" s="18" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="18" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="18" t="n">
-        <v/>
-      </c>
-      <c r="W17" s="18" t="n">
-        <v/>
-      </c>
-      <c r="X17" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Y17" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Z17" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AA17" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AB17" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AC17" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AD17" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AE17" s="18" t="inlineStr">
+      <c r="T17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="W17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="X17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Y17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Z17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AA17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AB17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AC17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AD17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AE17" s="2" t="inlineStr">
         <is>
           <t>正式填報</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>MOBG-2026-02358</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>沈彪/mo171026</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>2026-05-14 17:14:46</t>
         </is>
       </c>
-      <c r="E18" s="18" t="n">
-        <v/>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="E18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>資訊科技部</t>
         </is>
       </c>
-      <c r="G18" s="18" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>系統開發四團隊</t>
         </is>
       </c>
-      <c r="H18" s="18" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>MFT系統關於沙盒2項目需求投產</t>
         </is>
       </c>
-      <c r="I18" s="18" t="n">
-        <v/>
-      </c>
-      <c r="J18" s="18" t="inlineStr">
+      <c r="I18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>普通變更</t>
         </is>
       </c>
-      <c r="K18" s="18" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>應用-&gt;應用產品投產</t>
         </is>
       </c>
-      <c r="L18" s="18" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="18" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="18" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="18" t="inlineStr">
+      <c r="L18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>2026-05-21 18:00:00</t>
         </is>
       </c>
-      <c r="P18" s="18" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>2026-05-21 19:00:00</t>
         </is>
       </c>
-      <c r="Q18" s="18" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="18" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="18" t="inlineStr">
+      <c r="Q18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="T18" s="18" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="18" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="18" t="n">
-        <v/>
-      </c>
-      <c r="W18" s="18" t="n">
-        <v/>
-      </c>
-      <c r="X18" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Y18" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Z18" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AA18" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AB18" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AC18" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AD18" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AE18" s="18" t="inlineStr">
+      <c r="T18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="W18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="X18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Y18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Z18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AA18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AB18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AC18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AD18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AE18" s="2" t="inlineStr">
         <is>
           <t>正式填報</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>MOBG-2026-02331</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>黃君豪/mo159832</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>2026-05-14 09:23:52</t>
         </is>
       </c>
-      <c r="E19" s="18" t="n">
-        <v/>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="E19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>資訊科技部</t>
         </is>
       </c>
-      <c r="G19" s="18" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>系統開發五團隊</t>
         </is>
       </c>
-      <c r="H19" s="18" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>关于沙盒二項目手機銀行及BOCPAY的需求投产</t>
         </is>
       </c>
-      <c r="I19" s="18" t="n">
-        <v/>
-      </c>
-      <c r="J19" s="18" t="inlineStr">
+      <c r="I19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>普通變更</t>
         </is>
       </c>
-      <c r="K19" s="18" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>系統-&gt;系統版本升級</t>
         </is>
       </c>
-      <c r="L19" s="18" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="18" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="18" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="18" t="inlineStr">
+      <c r="L19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>2026-05-24 01:30:00</t>
         </is>
       </c>
-      <c r="P19" s="18" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>2026-05-24 06:00:00</t>
         </is>
       </c>
-      <c r="Q19" s="18" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>DBP-手機銀行,BCP-BOCPAY平台</t>
         </is>
       </c>
-      <c r="R19" s="18" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="18" t="inlineStr">
+      <c r="R19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="T19" s="18" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="18" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="18" t="n">
-        <v/>
-      </c>
-      <c r="W19" s="18" t="n">
-        <v/>
-      </c>
-      <c r="X19" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Y19" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Z19" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AA19" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AB19" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AC19" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AD19" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AE19" s="18" t="inlineStr">
+      <c r="T19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="W19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="X19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Y19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Z19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AA19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AB19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AC19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AD19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AE19" s="2" t="inlineStr">
         <is>
           <t>正式填報</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>MOBG-2026-02330</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>葉俊濠/mo174319</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>2026-05-13 16:41:44</t>
         </is>
       </c>
-      <c r="E20" s="18" t="n">
-        <v/>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
+      <c r="E20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>資訊科技部</t>
         </is>
       </c>
-      <c r="G20" s="18" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>系統開發二團隊</t>
         </is>
       </c>
-      <c r="H20" s="18" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>DWS系统关于補跑26年4月利息補貼報表數據</t>
         </is>
       </c>
-      <c r="I20" s="18" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>變更原因：本月新增「抗疫貸」利息補貼戶中合共103戶需補回2026年4月及之前還款數據報送金管局，由於筆數較多，為免手工錄入產生數據風險。
 變更主要內容：執行腳本插入相關數據到子集目標表
@@ -3331,139 +2953,139 @@
 漏洞扫描情况（新增服务器、系统和中间件升级等变更请提前联系安全团队进行漏洞扫描）</t>
         </is>
       </c>
-      <c r="J20" s="18" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>普通變更</t>
         </is>
       </c>
-      <c r="K20" s="18" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>應用-&gt;其他變更</t>
         </is>
       </c>
-      <c r="L20" s="18" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>請求</t>
         </is>
       </c>
-      <c r="M20" s="18" t="n">
-        <v/>
-      </c>
-      <c r="N20" s="18" t="n">
-        <v/>
-      </c>
-      <c r="O20" s="18" t="inlineStr">
+      <c r="M20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>2026-05-21 18:00:00</t>
         </is>
       </c>
-      <c r="P20" s="18" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>2026-05-21 18:30:00</t>
         </is>
       </c>
-      <c r="Q20" s="18" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>DWS-數據子集</t>
         </is>
       </c>
-      <c r="R20" s="18" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="S20" s="18" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="T20" s="18" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="18" t="inlineStr">
+      <c r="T20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="V20" s="18" t="n">
-        <v/>
-      </c>
-      <c r="W20" s="18" t="n">
-        <v/>
-      </c>
-      <c r="X20" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Y20" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Z20" s="18" t="inlineStr">
+      <c r="V20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="W20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="X20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Y20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA20" s="18" t="inlineStr">
+      <c r="AA20" s="2" t="inlineStr">
         <is>
           <t>中國銀行澳門分行/資訊科技部/應用運維團隊</t>
         </is>
       </c>
-      <c r="AB20" s="18" t="inlineStr">
+      <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>中國銀行澳門分行/資訊科技部/系統開發二團隊</t>
         </is>
       </c>
-      <c r="AC20" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AD20" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AE20" s="18" t="inlineStr">
+      <c r="AC20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AD20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AE20" s="2" t="inlineStr">
         <is>
           <t>執行人員指派</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>MOBG-2026-02321</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>林秋明/mo142409</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>2026-05-13 10:10:05</t>
         </is>
       </c>
-      <c r="E21" s="18" t="n">
-        <v/>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
+      <c r="E21" s="2" t="n">
+        <v/>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>資訊科技部</t>
         </is>
       </c>
-      <c r="G21" s="18" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>系統開發二團隊</t>
         </is>
       </c>
-      <c r="H21" s="18" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>ADC系统关于IBM Db2 拒绝服务漏洞(CVE-2025-36006) 的修復变更</t>
         </is>
       </c>
-      <c r="I21" s="18" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>變更原因：修復安全漏洞
 變更主要內容：換機升機DB, 包括遷移數據及修改上關聯系統配置
@@ -3473,350 +3095,350 @@
 漏洞扫描情况（新增服务器、系统和中间件升级等变更请提前联系安全团队进行漏洞扫描）不涉及</t>
         </is>
       </c>
-      <c r="J21" s="18" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>普通變更</t>
         </is>
       </c>
-      <c r="K21" s="18" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>系統-&gt;系統版本升級</t>
         </is>
       </c>
-      <c r="L21" s="18" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>請求</t>
         </is>
       </c>
-      <c r="M21" s="18" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="18" t="inlineStr">
+      <c r="M21" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">bladcdb1_rpa(apsuppt0)        ,bladcap1_rpa(apsuppt0)        ,budwsdb_dws(apsuppt0)         </t>
         </is>
       </c>
-      <c r="O21" s="18" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>2026-05-23 10:00:00</t>
         </is>
       </c>
-      <c r="P21" s="18" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>2026-05-23 11:30:00</t>
         </is>
       </c>
-      <c r="Q21" s="18" t="inlineStr">
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>ADC-信貸資料平臺前置系統,DWS-數據子集</t>
         </is>
       </c>
-      <c r="R21" s="18" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="S21" s="18" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="T21" s="18" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="18" t="inlineStr">
+      <c r="T21" s="2" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="V21" s="18" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>2026-05-23 10:00:00</t>
         </is>
       </c>
-      <c r="W21" s="18" t="inlineStr">
+      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>2026-05-23 11:30:00</t>
         </is>
       </c>
-      <c r="X21" s="18" t="inlineStr">
+      <c r="X21" s="2" t="inlineStr">
         <is>
           <t>90分钟</t>
         </is>
       </c>
-      <c r="Y21" s="18" t="inlineStr">
+      <c r="Y21" s="2" t="inlineStr">
         <is>
           <t>應用停止服務</t>
         </is>
       </c>
-      <c r="Z21" s="18" t="inlineStr">
+      <c r="Z21" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA21" s="18" t="inlineStr">
+      <c r="AA21" s="2" t="inlineStr">
         <is>
           <t>中國銀行澳門分行/資訊科技部/應用運維團隊</t>
         </is>
       </c>
-      <c r="AB21" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AC21" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AD21" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AE21" s="18" t="inlineStr">
+      <c r="AB21" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AC21" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AD21" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AE21" s="2" t="inlineStr">
         <is>
           <t>執行人員指派</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>MOBG-2026-02307</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>何子楓/mo149250</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>2026-05-11 14:34:04</t>
         </is>
       </c>
-      <c r="E22" s="18" t="n">
-        <v/>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
+      <c r="E22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>資訊科技部</t>
         </is>
       </c>
-      <c r="G22" s="18" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>系統開發一團隊</t>
         </is>
       </c>
-      <c r="H22" s="18" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>關於PMP服務器EOS下移Linux事的变更</t>
         </is>
       </c>
-      <c r="I22" s="18" t="n">
-        <v/>
-      </c>
-      <c r="J22" s="18" t="inlineStr">
+      <c r="I22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>普通變更</t>
         </is>
       </c>
-      <c r="K22" s="18" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>應用-&gt;應用產品投產</t>
         </is>
       </c>
-      <c r="L22" s="18" t="n">
-        <v/>
-      </c>
-      <c r="M22" s="18" t="n">
-        <v/>
-      </c>
-      <c r="N22" s="18" t="n">
-        <v/>
-      </c>
-      <c r="O22" s="18" t="inlineStr">
+      <c r="L22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>2026-05-24 03:00:00</t>
         </is>
       </c>
-      <c r="P22" s="18" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>2026-05-24 05:00:00</t>
         </is>
       </c>
-      <c r="Q22" s="18" t="inlineStr">
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>DDP-快捷支付系統</t>
         </is>
       </c>
-      <c r="R22" s="18" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="18" t="inlineStr">
+      <c r="R22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="T22" s="18" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
         <is>
           <t>陳冰清/mo159042</t>
         </is>
       </c>
-      <c r="U22" s="18" t="n">
-        <v/>
-      </c>
-      <c r="V22" s="18" t="n">
-        <v/>
-      </c>
-      <c r="W22" s="18" t="n">
-        <v/>
-      </c>
-      <c r="X22" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Y22" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Z22" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AA22" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AB22" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AC22" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AD22" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AE22" s="18" t="inlineStr">
+      <c r="U22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="W22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="X22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Y22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Z22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AA22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AB22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AC22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AD22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AE22" s="2" t="inlineStr">
         <is>
           <t>預填報</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>MOBG-2026-02305</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>柏志偉/mo159905</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>2026-05-11 10:07:41</t>
         </is>
       </c>
-      <c r="E23" s="18" t="n">
-        <v/>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
+      <c r="E23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>資訊科技部</t>
         </is>
       </c>
-      <c r="G23" s="18" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>系統開發二團隊</t>
         </is>
       </c>
-      <c r="H23" s="18" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>DQP系统关于DB2數據庫更新補丁的变更</t>
         </is>
       </c>
-      <c r="I23" s="18" t="n">
-        <v/>
-      </c>
-      <c r="J23" s="18" t="inlineStr">
+      <c r="I23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>普通變更</t>
         </is>
       </c>
-      <c r="K23" s="18" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>系統-&gt;系統補丁安裝</t>
         </is>
       </c>
-      <c r="L23" s="18" t="n">
-        <v/>
-      </c>
-      <c r="M23" s="18" t="n">
-        <v/>
-      </c>
-      <c r="N23" s="18" t="n">
-        <v/>
-      </c>
-      <c r="O23" s="18" t="inlineStr">
+      <c r="L23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>2026-05-24 02:00:00</t>
         </is>
       </c>
-      <c r="P23" s="18" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>2026-05-24 05:00:00</t>
         </is>
       </c>
-      <c r="Q23" s="18" t="inlineStr">
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>DQP-數據查詢接口服務平臺</t>
         </is>
       </c>
-      <c r="R23" s="18" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="18" t="inlineStr">
+      <c r="R23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="T23" s="18" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="18" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="18" t="n">
-        <v/>
-      </c>
-      <c r="W23" s="18" t="n">
-        <v/>
-      </c>
-      <c r="X23" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Y23" s="18" t="n">
-        <v/>
-      </c>
-      <c r="Z23" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AA23" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AB23" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AC23" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AD23" s="18" t="n">
-        <v/>
-      </c>
-      <c r="AE23" s="18" t="inlineStr">
+      <c r="T23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="W23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="X23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Y23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="Z23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AA23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AB23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AC23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AD23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="AE23" s="2" t="inlineStr">
         <is>
           <t>正式填報</t>
         </is>
